--- a/artifacts/SYNTHETIQUE.xlsx
+++ b/artifacts/SYNTHETIQUE.xlsx
@@ -10,8 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lisez-moi" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hypotheses" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historique" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modele" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Controles" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formules" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modele" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Controles" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="g_2026">'Hypotheses'!$C$3</definedName>
@@ -49,10 +50,10 @@
     <definedName name="pub_impot">'Historique'!$B$10</definedName>
     <definedName name="pub_minoritaires">'Historique'!$B$11</definedName>
     <definedName name="pub_net">'Historique'!$B$12</definedName>
-    <definedName name="impotRet">'Historique'!$D$24</definedName>
-    <definedName name="ajPub_ebitda">'Historique'!$B$31</definedName>
-    <definedName name="ajPub_ebit">'Historique'!$C$31</definedName>
-    <definedName name="ajPub_net">'Historique'!$D$31</definedName>
+    <definedName name="impotRet">'Historique'!$D$26</definedName>
+    <definedName name="ajPub_ebitda">'Historique'!$B$33</definedName>
+    <definedName name="ajPub_ebit">'Historique'!$C$33</definedName>
+    <definedName name="ajPub_net">'Historique'!$D$33</definedName>
     <definedName name="CA_2025">'Modele'!$B$3</definedName>
     <definedName name="CA_2026">'Modele'!$C$3</definedName>
     <definedName name="CA_2027">'Modele'!$D$3</definedName>
@@ -163,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -180,9 +181,14 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1509,7 +1515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1524,15 +1530,11 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ECHELLE PUBLIEE 2025-FY — un modele unique, les barreaux non publies restent vides</t>
+          <t>ECHELLE PUBLIEE — un modele unique, les barreaux non publies restent vides</t>
         </is>
       </c>
       <c r="B1" s="4" t="n"/>
       <c r="C1" s="4" t="n"/>
-      <c r="D1" s="4" t="n"/>
-      <c r="E1" s="4" t="n"/>
-      <c r="F1" s="4" t="n"/>
-      <c r="G1" s="4" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -1542,7 +1544,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>publie</t>
+          <t>2025-FY</t>
         </is>
       </c>
     </row>
@@ -1649,346 +1651,356 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>Taux d'impot effectif observe</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
           <t>IDENTITES DE L'ECHELLE</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>ebitda + da = ebit</t>
         </is>
       </c>
-      <c r="B15" s="13">
+      <c r="B17" s="14">
         <f>pub_ebitda+pub_da-pub_ebit</f>
         <v/>
       </c>
-      <c r="C15" s="2">
-        <f>IF(ABS(B15)&lt;=MAX(1,ABS(pub_ebit)*0.005),"OK","ECART")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="C17" s="2">
+        <f>IF(ABS(B17)&lt;=MAX(1,ABS(pub_ebit)*0.005),"OK","ECART")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>ebit + finNet = avantImpot</t>
         </is>
       </c>
-      <c r="B16" s="13">
+      <c r="B18" s="14">
         <f>pub_ebit+pub_finNet-pub_avantImpot</f>
         <v/>
       </c>
-      <c r="C16" s="2">
-        <f>IF(ABS(B16)&lt;=MAX(1,ABS(pub_avantImpot)*0.005),"OK","ECART")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="C18" s="2">
+        <f>IF(ABS(B18)&lt;=MAX(1,ABS(pub_avantImpot)*0.005),"OK","ECART")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>avantImpot + impot + minoritaires = net</t>
         </is>
       </c>
-      <c r="B17" s="13">
+      <c r="B19" s="14">
         <f>pub_avantImpot+pub_impot+pub_minoritaires-pub_net</f>
         <v/>
       </c>
-      <c r="C17" s="2">
-        <f>IF(ABS(B17)&lt;=MAX(1,ABS(pub_net)*0.005),"OK","ECART")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="C19" s="2">
+        <f>IF(ABS(B19)&lt;=MAX(1,ABS(pub_net)*0.005),"OK","ECART")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>RETRAITEMENTS — la table de l'emetteur, ligne a ligne</t>
         </is>
       </c>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="n"/>
-      <c r="F19" s="4" t="n"/>
-      <c r="G19" s="4" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>ligne</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>ebit</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>net</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>classe</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>origine</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>libelle</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>restructuration-2025</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="C21" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="D21" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>oneOff</t>
-        </is>
-      </c>
-      <c r="F21" s="12" t="inlineStr">
-        <is>
-          <t>emetteur</t>
-        </is>
-      </c>
-      <c r="G21" s="12" t="inlineStr">
-        <is>
-          <t>One-off restructuring costs</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>alpha-ppa-amort</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="D22" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>recurrent</t>
-        </is>
-      </c>
-      <c r="F22" s="12" t="inlineStr">
-        <is>
-          <t>emetteur</t>
-        </is>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>Amortisation of intangibles from the Alpha PPA</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>alpha-dette-interets</t>
+          <t>restructuration-2025</t>
         </is>
       </c>
       <c r="B23" s="11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="E23" s="12" t="inlineStr">
-        <is>
-          <t>recurrent</t>
-        </is>
-      </c>
-      <c r="F23" s="12" t="inlineStr">
+        <v>12</v>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>oneOff</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
         <is>
           <t>emetteur</t>
         </is>
       </c>
-      <c r="G23" s="12" t="inlineStr">
-        <is>
-          <t>Interest on the Alpha acquisition debt</t>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>One-off restructuring costs</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
+          <t>alpha-ppa-amort</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>recurrent</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t>emetteur</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>Amortisation of intangibles from the Alpha PPA</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>alpha-dette-interets</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>recurrent</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>emetteur</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>Interest on the Alpha acquisition debt</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
           <t>impot sur retraitements</t>
         </is>
       </c>
-      <c r="D24" s="14" t="n">
+      <c r="D26" s="15" t="n">
         <v>-17</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
         <is>
           <t>LES TROIS BASES — calculees, jamais saisies</t>
         </is>
       </c>
-      <c r="B26" s="4" t="n"/>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="4" t="n"/>
-      <c r="E26" s="4" t="n"/>
-      <c r="F26" s="4" t="n"/>
-      <c r="G26" s="4" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>base</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>ebit</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>net</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>moteur (net)</t>
         </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>Omnium (publie + vrais one-offs)</t>
-        </is>
-      </c>
-      <c r="B28" s="11">
-        <f>pub_ebitda+SUMIF($E$21:$E$23,"oneOff",B$21:B$23)</f>
-        <v/>
-      </c>
-      <c r="C28" s="11">
-        <f>pub_ebit+SUMIF($E$21:$E$23,"oneOff",C$21:C$23)</f>
-        <v/>
-      </c>
-      <c r="D28" s="11">
-        <f>pub_net+SUMIF($E$21:$E$23,"oneOff",D$21:D$23)+impotRet*SUMIF($E$21:$E$23,"oneOff",$D$21:$D$23)/SUM($D$21:$D$23)</f>
-        <v/>
-      </c>
-      <c r="E28" s="12" t="n">
-        <v>107.75</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>Ajuste du management (+ recurrents)</t>
-        </is>
-      </c>
-      <c r="B29" s="11">
-        <f>pub_ebitda+SUM(B$21:B$23)</f>
-        <v/>
-      </c>
-      <c r="C29" s="11">
-        <f>pub_ebit+SUM(C$21:C$23)</f>
-        <v/>
-      </c>
-      <c r="D29" s="11">
-        <f>pub_net+SUM(D$21:D$23)+impotRet</f>
-        <v/>
-      </c>
-      <c r="E29" s="12" t="n">
-        <v>131</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
+          <t>Omnium (publie + vrais one-offs)</t>
+        </is>
+      </c>
+      <c r="B30" s="11">
+        <f>pub_ebitda+SUMIF($E$23:$E$25,"oneOff",B$23:B$25)</f>
+        <v/>
+      </c>
+      <c r="C30" s="11">
+        <f>pub_ebit+SUMIF($E$23:$E$25,"oneOff",C$23:C$25)</f>
+        <v/>
+      </c>
+      <c r="D30" s="11">
+        <f>pub_net+SUMIF($E$23:$E$25,"oneOff",D$23:D$25)+impotRet*SUMIF($E$23:$E$25,"oneOff",$D$23:$D$25)/SUM($D$23:$D$25)</f>
+        <v/>
+      </c>
+      <c r="E30" s="13" t="n">
+        <v>107.75</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>Ajuste du management (+ recurrents)</t>
+        </is>
+      </c>
+      <c r="B31" s="11">
+        <f>pub_ebitda+SUM(B$23:B$25)</f>
+        <v/>
+      </c>
+      <c r="C31" s="11">
+        <f>pub_ebit+SUM(C$23:C$25)</f>
+        <v/>
+      </c>
+      <c r="D31" s="11">
+        <f>pub_net+SUM(D$23:D$25)+impotRet</f>
+        <v/>
+      </c>
+      <c r="E31" s="13" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
           <t>Coin = recurrents-deguises</t>
         </is>
       </c>
-      <c r="B30" s="11">
-        <f>SUMIF($E$21:$E$23,"recurrent",B$21:B$23)</f>
-        <v/>
-      </c>
-      <c r="C30" s="11">
-        <f>SUMIF($E$21:$E$23,"recurrent",C$21:C$23)</f>
-        <v/>
-      </c>
-      <c r="D30" s="11">
-        <f>SUMIF($E$21:$E$23,"recurrent",D$21:D$23)+impotRet*SUMIF($E$21:$E$23,"recurrent",$D$21:$D$23)/SUM($D$21:$D$23)</f>
-        <v/>
-      </c>
-      <c r="E30" s="12" t="n">
+      <c r="B32" s="11">
+        <f>SUMIF($E$23:$E$25,"recurrent",B$23:B$25)</f>
+        <v/>
+      </c>
+      <c r="C32" s="11">
+        <f>SUMIF($E$23:$E$25,"recurrent",C$23:C$25)</f>
+        <v/>
+      </c>
+      <c r="D32" s="11">
+        <f>SUMIF($E$23:$E$25,"recurrent",D$23:D$25)+impotRet*SUMIF($E$23:$E$25,"recurrent",$D$23:$D$25)/SUM($D$23:$D$25)</f>
+        <v/>
+      </c>
+      <c r="E32" s="13" t="n">
         <v>23.25</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>ajuste PUBLIE par la societe (cible de bouclage)</t>
         </is>
       </c>
-      <c r="B31" s="11" t="n">
+      <c r="B33" s="11" t="n">
         <v>262</v>
       </c>
-      <c r="C31" s="11" t="n">
+      <c r="C33" s="11" t="n">
         <v>202</v>
       </c>
-      <c r="D31" s="11" t="n">
+      <c r="D33" s="11" t="n">
         <v>131</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>BOUCLAGE</t>
         </is>
       </c>
-      <c r="B32" s="2">
-        <f>IF(ABS(B30-ajPub_ebitda)&lt;=MAX(1,ABS(ajPub_ebitda)*0.005),"OK","NE BOUCLE PAS")</f>
-        <v/>
-      </c>
-      <c r="C32" s="2">
-        <f>IF(ABS(C30-ajPub_ebit)&lt;=MAX(1,ABS(ajPub_ebit)*0.005),"OK","NE BOUCLE PAS")</f>
-        <v/>
-      </c>
-      <c r="D32" s="2">
-        <f>IF(ABS(D30-ajPub_net)&lt;=MAX(1,ABS(ajPub_net)*0.005),"OK","NE BOUCLE PAS")</f>
+      <c r="B34" s="2">
+        <f>IF(ABS(B32-ajPub_ebitda)&lt;=MAX(1,ABS(ajPub_ebitda)*0.005),"OK","NE BOUCLE PAS")</f>
+        <v/>
+      </c>
+      <c r="C34" s="2">
+        <f>IF(ABS(C32-ajPub_ebit)&lt;=MAX(1,ABS(ajPub_ebit)*0.005),"OK","NE BOUCLE PAS")</f>
+        <v/>
+      </c>
+      <c r="D34" s="2">
+        <f>IF(ABS(D32-ajPub_net)&lt;=MAX(1,ABS(ajPub_net)*0.005),"OK","NE BOUCLE PAS")</f>
         <v/>
       </c>
     </row>
@@ -1998,6 +2010,339 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="84" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>FORMULES DU MODELE — l'ecriture du calcul, ligne par ligne</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="n"/>
+      <c r="C1" s="4" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>ligne</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>calcul</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>formule posee sur 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Chiffre d'affaires</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>CA(n) = CA(n-1) x (1 + g_n)</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>'=B3*(1+g_2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>EBITDA(n) = CA(n) x marge_n</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>'=C3*C5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>dotations hors PPA</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>dotHorsPPA(n) = dotHorsPPA(n-1) + CA(n-1) x capexRatio / dureeAmort</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>'=B7+B3*capexRatio/dureeAmort</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>Dotations</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>dotations(n) = -( dotHorsPPA(n) + amortPPA(n) )</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>'=-(C7+C8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>EBIT(n) = EBITDA(n) + dotations(n)</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>'=C6+C9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Resultat financier (rang 2)</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>resultatFinancier(n) = -detteBrute(n-1) x tauxDette + tresorerie(n-1) x tauxCash - detteLocative(n-1) x tauxLease   [rang 2]</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>'=-(B11*tauxDette)+B12*tauxCash-(B13*tauxLease)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>Resultat avant impot</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>avantImpot(n) = EBIT(n) + resultatFinancier(n)</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>'=C10+C14</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>Impot</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>impot(n) = -avantImpot(n) x tauxIS_n   [ou OVERRIDE declare]</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>'=-C15*C16</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>Minoritaires</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>minoritaires(n) = partMinos x ( avantImpot(n) + impot(n) )</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>'=partMinos*(C15+C17)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>Resultat net</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>net(n) = avantImpot(n) + impot(n) + minoritaires(n)</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>'=C15+C17+C18</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>Actions (millions)</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>actions(n) = actions(n-1) x (1 - rachatPct)</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>'=B20*(1-rachatPct)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>BPA</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>BPA(n) = net(n) / actions(n)</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>'=C19/C20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>Dividende verse</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>dividende(n) = net(n) x tauxDistrib</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>'=C19*tauxDistrib</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>OU LIRE LE RESTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Hypotheses</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>la valeur de chaque moteur, son rang de provenance et sa peremption</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Historique</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>l'echelle publiee de chaque exercice, ses identites, et les trois bases</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Modele</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>le deroule annee par annee ; la colonne de droite porte la valeur du moteur Python</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Controles</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>formule contre moteur, cellule a cellule</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>engine/model.py</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>la SOURCE des formules ci-dessus — le classeur n'en est que le miroir</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2044,34 +2389,34 @@
       <c r="B2" s="5" t="n">
         <v>2025</v>
       </c>
-      <c r="C2" s="15" t="n">
+      <c r="C2" s="18" t="n">
         <v>2026</v>
       </c>
-      <c r="D2" s="15" t="n">
+      <c r="D2" s="18" t="n">
         <v>2027</v>
       </c>
-      <c r="E2" s="15" t="n">
+      <c r="E2" s="18" t="n">
         <v>2028</v>
       </c>
-      <c r="F2" s="15" t="n">
+      <c r="F2" s="18" t="n">
         <v>2029</v>
       </c>
-      <c r="G2" s="15" t="n">
+      <c r="G2" s="18" t="n">
         <v>2030</v>
       </c>
-      <c r="I2" s="12" t="n">
+      <c r="I2" s="13" t="n">
         <v>2026</v>
       </c>
-      <c r="J2" s="12" t="n">
+      <c r="J2" s="13" t="n">
         <v>2027</v>
       </c>
-      <c r="K2" s="12" t="n">
+      <c r="K2" s="13" t="n">
         <v>2028</v>
       </c>
-      <c r="L2" s="12" t="n">
+      <c r="L2" s="13" t="n">
         <v>2029</v>
       </c>
-      <c r="M2" s="12" t="n">
+      <c r="M2" s="13" t="n">
         <v>2030</v>
       </c>
     </row>
@@ -2084,39 +2429,39 @@
       <c r="B3" s="11" t="n">
         <v>1000</v>
       </c>
-      <c r="C3" s="16">
+      <c r="C3" s="19">
         <f>B3*(1+g_2026)</f>
         <v/>
       </c>
-      <c r="D3" s="16">
+      <c r="D3" s="19">
         <f>C3*(1+g_2027)</f>
         <v/>
       </c>
-      <c r="E3" s="16">
+      <c r="E3" s="19">
         <f>D3*(1+g_2028)</f>
         <v/>
       </c>
-      <c r="F3" s="16">
+      <c r="F3" s="19">
         <f>E3*(1+g_2029)</f>
         <v/>
       </c>
-      <c r="G3" s="16">
+      <c r="G3" s="19">
         <f>F3*(1+g_2030)</f>
         <v/>
       </c>
-      <c r="I3" s="17" t="n">
+      <c r="I3" s="20" t="n">
         <v>1070</v>
       </c>
-      <c r="J3" s="17" t="n">
+      <c r="J3" s="20" t="n">
         <v>1134.2</v>
       </c>
-      <c r="K3" s="17" t="n">
+      <c r="K3" s="20" t="n">
         <v>1196.581</v>
       </c>
-      <c r="L3" s="17" t="n">
+      <c r="L3" s="20" t="n">
         <v>1256.41</v>
       </c>
-      <c r="M3" s="17" t="n">
+      <c r="M3" s="20" t="n">
         <v>1312.9485</v>
       </c>
     </row>
@@ -2126,39 +2471,39 @@
           <t>Croissance</t>
         </is>
       </c>
-      <c r="C4" s="18">
+      <c r="C4" s="21">
         <f>g_2026</f>
         <v/>
       </c>
-      <c r="D4" s="18">
+      <c r="D4" s="21">
         <f>g_2027</f>
         <v/>
       </c>
-      <c r="E4" s="18">
+      <c r="E4" s="21">
         <f>g_2028</f>
         <v/>
       </c>
-      <c r="F4" s="18">
+      <c r="F4" s="21">
         <f>g_2029</f>
         <v/>
       </c>
-      <c r="G4" s="18">
+      <c r="G4" s="21">
         <f>g_2030</f>
         <v/>
       </c>
-      <c r="I4" s="19" t="n">
+      <c r="I4" s="22" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="J4" s="19" t="n">
+      <c r="J4" s="22" t="n">
         <v>0.06</v>
       </c>
-      <c r="K4" s="19" t="n">
+      <c r="K4" s="22" t="n">
         <v>0.055</v>
       </c>
-      <c r="L4" s="19" t="n">
+      <c r="L4" s="22" t="n">
         <v>0.05</v>
       </c>
-      <c r="M4" s="19" t="n">
+      <c r="M4" s="22" t="n">
         <v>0.045</v>
       </c>
     </row>
@@ -2168,39 +2513,39 @@
           <t>Marge d'EBITDA</t>
         </is>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="21">
         <f>marge_2026</f>
         <v/>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="21">
         <f>marge_2027</f>
         <v/>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="21">
         <f>marge_2028</f>
         <v/>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="21">
         <f>marge_2029</f>
         <v/>
       </c>
-      <c r="G5" s="18">
+      <c r="G5" s="21">
         <f>marge_2030</f>
         <v/>
       </c>
-      <c r="I5" s="19" t="n">
+      <c r="I5" s="22" t="n">
         <v>0.262</v>
       </c>
-      <c r="J5" s="19" t="n">
+      <c r="J5" s="22" t="n">
         <v>0.268</v>
       </c>
-      <c r="K5" s="19" t="n">
+      <c r="K5" s="22" t="n">
         <v>0.274</v>
       </c>
-      <c r="L5" s="19" t="n">
+      <c r="L5" s="22" t="n">
         <v>0.28</v>
       </c>
-      <c r="M5" s="19" t="n">
+      <c r="M5" s="22" t="n">
         <v>0.285</v>
       </c>
     </row>
@@ -2213,39 +2558,39 @@
       <c r="B6" s="11" t="n">
         <v>250</v>
       </c>
-      <c r="C6" s="16">
+      <c r="C6" s="19">
         <f>C3*C5</f>
         <v/>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="19">
         <f>D3*D5</f>
         <v/>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="19">
         <f>E3*E5</f>
         <v/>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="19">
         <f>F3*F5</f>
         <v/>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="19">
         <f>G3*G5</f>
         <v/>
       </c>
-      <c r="I6" s="17" t="n">
+      <c r="I6" s="20" t="n">
         <v>280.34</v>
       </c>
-      <c r="J6" s="17" t="n">
+      <c r="J6" s="20" t="n">
         <v>303.9656</v>
       </c>
-      <c r="K6" s="17" t="n">
+      <c r="K6" s="20" t="n">
         <v>327.8632</v>
       </c>
-      <c r="L6" s="17" t="n">
+      <c r="L6" s="20" t="n">
         <v>351.7948</v>
       </c>
-      <c r="M6" s="17" t="n">
+      <c r="M6" s="20" t="n">
         <v>374.1903</v>
       </c>
     </row>
@@ -2258,39 +2603,39 @@
       <c r="B7" s="11" t="n">
         <v>90</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="19">
         <f>B7+B3*capexRatio/dureeAmort</f>
         <v/>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="19">
         <f>C7+C3*capexRatio/dureeAmort</f>
         <v/>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="19">
         <f>D7+D3*capexRatio/dureeAmort</f>
         <v/>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="19">
         <f>E7+E3*capexRatio/dureeAmort</f>
         <v/>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="19">
         <f>F7+F3*capexRatio/dureeAmort</f>
         <v/>
       </c>
-      <c r="I7" s="17" t="n">
+      <c r="I7" s="20" t="n">
         <v>97.5</v>
       </c>
-      <c r="J7" s="17" t="n">
+      <c r="J7" s="20" t="n">
         <v>105.525</v>
       </c>
-      <c r="K7" s="17" t="n">
+      <c r="K7" s="20" t="n">
         <v>114.0315</v>
       </c>
-      <c r="L7" s="17" t="n">
+      <c r="L7" s="20" t="n">
         <v>123.0059</v>
       </c>
-      <c r="M7" s="17" t="n">
+      <c r="M7" s="20" t="n">
         <v>132.4289</v>
       </c>
     </row>
@@ -2303,39 +2648,39 @@
       <c r="B8" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="19">
         <f>30.0</f>
         <v/>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="19">
         <f>28.0</f>
         <v/>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="19">
         <f>24.0</f>
         <v/>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="19">
         <f>18.0</f>
         <v/>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="19">
         <f>10.0</f>
         <v/>
       </c>
-      <c r="I8" s="17" t="n">
+      <c r="I8" s="20" t="n">
         <v>30</v>
       </c>
-      <c r="J8" s="17" t="n">
+      <c r="J8" s="20" t="n">
         <v>28</v>
       </c>
-      <c r="K8" s="17" t="n">
+      <c r="K8" s="20" t="n">
         <v>24</v>
       </c>
-      <c r="L8" s="17" t="n">
+      <c r="L8" s="20" t="n">
         <v>18</v>
       </c>
-      <c r="M8" s="17" t="n">
+      <c r="M8" s="20" t="n">
         <v>10</v>
       </c>
     </row>
@@ -2348,39 +2693,39 @@
       <c r="B9" s="11" t="n">
         <v>-90</v>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="19">
         <f>-(C7+C8)</f>
         <v/>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="19">
         <f>-(D7+D8)</f>
         <v/>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="19">
         <f>-(E7+E8)</f>
         <v/>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="19">
         <f>-(F7+F8)</f>
         <v/>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="19">
         <f>-(G7+G8)</f>
         <v/>
       </c>
-      <c r="I9" s="17" t="n">
+      <c r="I9" s="20" t="n">
         <v>-127.5</v>
       </c>
-      <c r="J9" s="17" t="n">
+      <c r="J9" s="20" t="n">
         <v>-133.525</v>
       </c>
-      <c r="K9" s="17" t="n">
+      <c r="K9" s="20" t="n">
         <v>-138.0315</v>
       </c>
-      <c r="L9" s="17" t="n">
+      <c r="L9" s="20" t="n">
         <v>-141.0059</v>
       </c>
-      <c r="M9" s="17" t="n">
+      <c r="M9" s="20" t="n">
         <v>-142.4289</v>
       </c>
     </row>
@@ -2393,39 +2738,39 @@
       <c r="B10" s="11" t="n">
         <v>160</v>
       </c>
-      <c r="C10" s="16">
+      <c r="C10" s="19">
         <f>C6+C9</f>
         <v/>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="19">
         <f>D6+D9</f>
         <v/>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="19">
         <f>E6+E9</f>
         <v/>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="19">
         <f>F6+F9</f>
         <v/>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="19">
         <f>G6+G9</f>
         <v/>
       </c>
-      <c r="I10" s="17" t="n">
+      <c r="I10" s="20" t="n">
         <v>152.84</v>
       </c>
-      <c r="J10" s="17" t="n">
+      <c r="J10" s="20" t="n">
         <v>170.4406</v>
       </c>
-      <c r="K10" s="17" t="n">
+      <c r="K10" s="20" t="n">
         <v>189.8317</v>
       </c>
-      <c r="L10" s="17" t="n">
+      <c r="L10" s="20" t="n">
         <v>210.789</v>
       </c>
-      <c r="M10" s="17" t="n">
+      <c r="M10" s="20" t="n">
         <v>231.7614</v>
       </c>
     </row>
@@ -2438,23 +2783,23 @@
       <c r="B11" s="11" t="n">
         <v>520</v>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="19">
         <f>B11</f>
         <v/>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="19">
         <f>C11</f>
         <v/>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="19">
         <f>D11</f>
         <v/>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="19">
         <f>E11</f>
         <v/>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="19">
         <f>F11</f>
         <v/>
       </c>
@@ -2468,23 +2813,23 @@
       <c r="B12" s="11" t="n">
         <v>120</v>
       </c>
-      <c r="C12" s="16">
+      <c r="C12" s="19">
         <f>B12+C19-C22-B3*capexRatio-C9</f>
         <v/>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="19">
         <f>C12+D19-D22-C3*capexRatio-D9</f>
         <v/>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="19">
         <f>D12+E19-E22-D3*capexRatio-E9</f>
         <v/>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="19">
         <f>E12+F19-F22-E3*capexRatio-F9</f>
         <v/>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="19">
         <f>F12+G19-G22-F3*capexRatio-G9</f>
         <v/>
       </c>
@@ -2498,23 +2843,23 @@
       <c r="B13" s="11" t="n">
         <v>60</v>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="19">
         <f>B13</f>
         <v/>
       </c>
-      <c r="D13" s="16">
+      <c r="D13" s="19">
         <f>C13</f>
         <v/>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="19">
         <f>D13</f>
         <v/>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="19">
         <f>E13</f>
         <v/>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="19">
         <f>F13</f>
         <v/>
       </c>
@@ -2528,39 +2873,39 @@
       <c r="B14" s="11" t="n">
         <v>-20</v>
       </c>
-      <c r="C14" s="16">
+      <c r="C14" s="19">
         <f>-(B11*tauxDette)+B12*tauxCash-(B13*tauxLease)</f>
         <v/>
       </c>
-      <c r="D14" s="16">
+      <c r="D14" s="19">
         <f>-(C11*tauxDette)+C12*tauxCash-(C13*tauxLease)</f>
         <v/>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="19">
         <f>-(D11*tauxDette)+D12*tauxCash-(D13*tauxLease)</f>
         <v/>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="19">
         <f>-(E11*tauxDette)+E12*tauxCash-(E13*tauxLease)</f>
         <v/>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="19">
         <f>-(F11*tauxDette)+F12*tauxCash-(F13*tauxLease)</f>
         <v/>
       </c>
-      <c r="I14" s="17" t="n">
+      <c r="I14" s="20" t="n">
         <v>-21.54</v>
       </c>
-      <c r="J14" s="17" t="n">
+      <c r="J14" s="20" t="n">
         <v>-18.8628</v>
       </c>
-      <c r="K14" s="17" t="n">
+      <c r="K14" s="20" t="n">
         <v>-15.9744</v>
       </c>
-      <c r="L14" s="17" t="n">
+      <c r="L14" s="20" t="n">
         <v>-12.8522</v>
       </c>
-      <c r="M14" s="17" t="n">
+      <c r="M14" s="20" t="n">
         <v>-9.5067</v>
       </c>
     </row>
@@ -2573,39 +2918,39 @@
       <c r="B15" s="11" t="n">
         <v>140</v>
       </c>
-      <c r="C15" s="16">
+      <c r="C15" s="19">
         <f>C10+C14</f>
         <v/>
       </c>
-      <c r="D15" s="16">
+      <c r="D15" s="19">
         <f>D10+D14</f>
         <v/>
       </c>
-      <c r="E15" s="16">
+      <c r="E15" s="19">
         <f>E10+E14</f>
         <v/>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="19">
         <f>F10+F14</f>
         <v/>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="19">
         <f>G10+G14</f>
         <v/>
       </c>
-      <c r="I15" s="17" t="n">
+      <c r="I15" s="20" t="n">
         <v>131.3</v>
       </c>
-      <c r="J15" s="17" t="n">
+      <c r="J15" s="20" t="n">
         <v>151.5778</v>
       </c>
-      <c r="K15" s="17" t="n">
+      <c r="K15" s="20" t="n">
         <v>173.8573</v>
       </c>
-      <c r="L15" s="17" t="n">
+      <c r="L15" s="20" t="n">
         <v>197.9368</v>
       </c>
-      <c r="M15" s="17" t="n">
+      <c r="M15" s="20" t="n">
         <v>222.2547</v>
       </c>
     </row>
@@ -2615,39 +2960,39 @@
           <t>Taux d'impot applique</t>
         </is>
       </c>
-      <c r="C16" s="18">
+      <c r="C16" s="21">
         <f>tauxIS_2026</f>
         <v/>
       </c>
-      <c r="D16" s="18">
+      <c r="D16" s="21">
         <f>tauxIS_2027</f>
         <v/>
       </c>
-      <c r="E16" s="18">
+      <c r="E16" s="21">
         <f>tauxIS_2028</f>
         <v/>
       </c>
-      <c r="F16" s="18">
+      <c r="F16" s="21">
         <f>tauxIS_2029</f>
         <v/>
       </c>
-      <c r="G16" s="18">
+      <c r="G16" s="21">
         <f>tauxIS_2030</f>
         <v/>
       </c>
-      <c r="I16" s="19" t="n">
+      <c r="I16" s="22" t="n">
         <v>0.24</v>
       </c>
-      <c r="J16" s="19" t="n">
+      <c r="J16" s="22" t="n">
         <v>0.255</v>
       </c>
-      <c r="K16" s="19" t="n">
+      <c r="K16" s="22" t="n">
         <v>0.255</v>
       </c>
-      <c r="L16" s="19" t="n">
+      <c r="L16" s="22" t="n">
         <v>0.255</v>
       </c>
-      <c r="M16" s="19" t="n">
+      <c r="M16" s="22" t="n">
         <v>0.255</v>
       </c>
     </row>
@@ -2660,39 +3005,39 @@
       <c r="B17" s="11" t="n">
         <v>-35</v>
       </c>
-      <c r="C17" s="16">
+      <c r="C17" s="19">
         <f>-C15*C16</f>
         <v/>
       </c>
-      <c r="D17" s="16">
+      <c r="D17" s="19">
         <f>-D15*D16</f>
         <v/>
       </c>
-      <c r="E17" s="16">
+      <c r="E17" s="19">
         <f>-E15*E16</f>
         <v/>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="19">
         <f>-F15*F16</f>
         <v/>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="19">
         <f>-G15*G16</f>
         <v/>
       </c>
-      <c r="I17" s="17" t="n">
+      <c r="I17" s="20" t="n">
         <v>-31.512</v>
       </c>
-      <c r="J17" s="17" t="n">
+      <c r="J17" s="20" t="n">
         <v>-38.6523</v>
       </c>
-      <c r="K17" s="17" t="n">
+      <c r="K17" s="20" t="n">
         <v>-44.3336</v>
       </c>
-      <c r="L17" s="17" t="n">
+      <c r="L17" s="20" t="n">
         <v>-50.4739</v>
       </c>
-      <c r="M17" s="17" t="n">
+      <c r="M17" s="20" t="n">
         <v>-56.675</v>
       </c>
     </row>
@@ -2705,39 +3050,39 @@
       <c r="B18" s="11" t="n">
         <v>-5</v>
       </c>
-      <c r="C18" s="16">
+      <c r="C18" s="19">
         <f>partMinos*(C15+C17)</f>
         <v/>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="19">
         <f>partMinos*(D15+D17)</f>
         <v/>
       </c>
-      <c r="E18" s="16">
+      <c r="E18" s="19">
         <f>partMinos*(E15+E17)</f>
         <v/>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="19">
         <f>partMinos*(F15+F17)</f>
         <v/>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="19">
         <f>partMinos*(G15+G17)</f>
         <v/>
       </c>
-      <c r="I18" s="17" t="n">
+      <c r="I18" s="20" t="n">
         <v>-4.9894</v>
       </c>
-      <c r="J18" s="17" t="n">
+      <c r="J18" s="20" t="n">
         <v>-5.6463</v>
       </c>
-      <c r="K18" s="17" t="n">
+      <c r="K18" s="20" t="n">
         <v>-6.4762</v>
       </c>
-      <c r="L18" s="17" t="n">
+      <c r="L18" s="20" t="n">
         <v>-7.3731</v>
       </c>
-      <c r="M18" s="17" t="n">
+      <c r="M18" s="20" t="n">
         <v>-8.279</v>
       </c>
     </row>
@@ -2750,39 +3095,39 @@
       <c r="B19" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="C19" s="16">
+      <c r="C19" s="19">
         <f>C15+C17+C18</f>
         <v/>
       </c>
-      <c r="D19" s="16">
+      <c r="D19" s="19">
         <f>D15+D17+D18</f>
         <v/>
       </c>
-      <c r="E19" s="16">
+      <c r="E19" s="19">
         <f>E15+E17+E18</f>
         <v/>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="19">
         <f>F15+F17+F18</f>
         <v/>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="19">
         <f>G15+G17+G18</f>
         <v/>
       </c>
-      <c r="I19" s="17" t="n">
+      <c r="I19" s="20" t="n">
         <v>94.79859999999999</v>
       </c>
-      <c r="J19" s="17" t="n">
+      <c r="J19" s="20" t="n">
         <v>107.2792</v>
       </c>
-      <c r="K19" s="17" t="n">
+      <c r="K19" s="20" t="n">
         <v>123.0475</v>
       </c>
-      <c r="L19" s="17" t="n">
+      <c r="L19" s="20" t="n">
         <v>140.0898</v>
       </c>
-      <c r="M19" s="17" t="n">
+      <c r="M19" s="20" t="n">
         <v>157.3008</v>
       </c>
     </row>
@@ -2792,42 +3137,42 @@
           <t>Actions (millions)</t>
         </is>
       </c>
-      <c r="B20" s="20" t="n">
+      <c r="B20" s="23" t="n">
         <v>50</v>
       </c>
-      <c r="C20" s="21">
+      <c r="C20" s="24">
         <f>B20*(1-rachatPct)</f>
         <v/>
       </c>
-      <c r="D20" s="21">
+      <c r="D20" s="24">
         <f>C20*(1-rachatPct)</f>
         <v/>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="24">
         <f>D20*(1-rachatPct)</f>
         <v/>
       </c>
-      <c r="F20" s="21">
+      <c r="F20" s="24">
         <f>E20*(1-rachatPct)</f>
         <v/>
       </c>
-      <c r="G20" s="21">
+      <c r="G20" s="24">
         <f>F20*(1-rachatPct)</f>
         <v/>
       </c>
-      <c r="I20" s="22" t="n">
+      <c r="I20" s="25" t="n">
         <v>49.25</v>
       </c>
-      <c r="J20" s="22" t="n">
+      <c r="J20" s="25" t="n">
         <v>48.5112</v>
       </c>
-      <c r="K20" s="22" t="n">
+      <c r="K20" s="25" t="n">
         <v>47.7836</v>
       </c>
-      <c r="L20" s="22" t="n">
+      <c r="L20" s="25" t="n">
         <v>47.0668</v>
       </c>
-      <c r="M20" s="22" t="n">
+      <c r="M20" s="25" t="n">
         <v>46.3608</v>
       </c>
     </row>
@@ -2837,42 +3182,42 @@
           <t>BPA</t>
         </is>
       </c>
-      <c r="B21" s="20" t="n">
+      <c r="B21" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="C21" s="21">
+      <c r="C21" s="24">
         <f>C19/C20</f>
         <v/>
       </c>
-      <c r="D21" s="21">
+      <c r="D21" s="24">
         <f>D19/D20</f>
         <v/>
       </c>
-      <c r="E21" s="21">
+      <c r="E21" s="24">
         <f>E19/E20</f>
         <v/>
       </c>
-      <c r="F21" s="21">
+      <c r="F21" s="24">
         <f>F19/F20</f>
         <v/>
       </c>
-      <c r="G21" s="21">
+      <c r="G21" s="24">
         <f>G19/G20</f>
         <v/>
       </c>
-      <c r="I21" s="22" t="n">
+      <c r="I21" s="25" t="n">
         <v>1.9248</v>
       </c>
-      <c r="J21" s="22" t="n">
+      <c r="J21" s="25" t="n">
         <v>2.2114</v>
       </c>
-      <c r="K21" s="22" t="n">
+      <c r="K21" s="25" t="n">
         <v>2.5751</v>
       </c>
-      <c r="L21" s="22" t="n">
+      <c r="L21" s="25" t="n">
         <v>2.9764</v>
       </c>
-      <c r="M21" s="22" t="n">
+      <c r="M21" s="25" t="n">
         <v>3.393</v>
       </c>
     </row>
@@ -2882,39 +3227,39 @@
           <t>Dividende verse</t>
         </is>
       </c>
-      <c r="C22" s="16">
+      <c r="C22" s="19">
         <f>C19*tauxDistrib</f>
         <v/>
       </c>
-      <c r="D22" s="16">
+      <c r="D22" s="19">
         <f>D19*tauxDistrib</f>
         <v/>
       </c>
-      <c r="E22" s="16">
+      <c r="E22" s="19">
         <f>E19*tauxDistrib</f>
         <v/>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="19">
         <f>F19*tauxDistrib</f>
         <v/>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="19">
         <f>G19*tauxDistrib</f>
         <v/>
       </c>
-      <c r="I22" s="17" t="n">
+      <c r="I22" s="20" t="n">
         <v>28.4396</v>
       </c>
-      <c r="J22" s="17" t="n">
+      <c r="J22" s="20" t="n">
         <v>32.1838</v>
       </c>
-      <c r="K22" s="17" t="n">
+      <c r="K22" s="20" t="n">
         <v>36.9142</v>
       </c>
-      <c r="L22" s="17" t="n">
+      <c r="L22" s="20" t="n">
         <v>42.0269</v>
       </c>
-      <c r="M22" s="17" t="n">
+      <c r="M22" s="20" t="n">
         <v>47.1902</v>
       </c>
     </row>
@@ -2926,128 +3271,128 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">  croissance</t>
         </is>
       </c>
-      <c r="C25" s="23" t="inlineStr">
+      <c r="C25" s="26" t="inlineStr">
         <is>
           <t>guidance</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>normatif</t>
         </is>
       </c>
-      <c r="E25" s="12" t="inlineStr">
+      <c r="E25" s="13" t="inlineStr">
         <is>
           <t>normatif</t>
         </is>
       </c>
-      <c r="F25" s="12" t="inlineStr">
+      <c r="F25" s="13" t="inlineStr">
         <is>
           <t>normatif</t>
         </is>
       </c>
-      <c r="G25" s="12" t="inlineStr">
+      <c r="G25" s="13" t="inlineStr">
         <is>
           <t>normatif</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">  marge</t>
         </is>
       </c>
-      <c r="C26" s="23" t="inlineStr">
+      <c r="C26" s="26" t="inlineStr">
         <is>
           <t>guidance</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D26" s="13" t="inlineStr">
         <is>
           <t>implicite</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+      <c r="E26" s="13" t="inlineStr">
         <is>
           <t>implicite</t>
         </is>
       </c>
-      <c r="F26" s="12" t="inlineStr">
+      <c r="F26" s="13" t="inlineStr">
         <is>
           <t>implicite</t>
         </is>
       </c>
-      <c r="G26" s="12" t="inlineStr">
+      <c r="G26" s="13" t="inlineStr">
         <is>
           <t>implicite</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">  taux d'impot</t>
         </is>
       </c>
-      <c r="C27" s="23" t="inlineStr">
+      <c r="C27" s="26" t="inlineStr">
         <is>
           <t>guidance</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr">
+      <c r="D27" s="13" t="inlineStr">
         <is>
           <t>normatif</t>
         </is>
       </c>
-      <c r="E27" s="12" t="inlineStr">
+      <c r="E27" s="13" t="inlineStr">
         <is>
           <t>normatif</t>
         </is>
       </c>
-      <c r="F27" s="12" t="inlineStr">
+      <c r="F27" s="13" t="inlineStr">
         <is>
           <t>normatif</t>
         </is>
       </c>
-      <c r="G27" s="12" t="inlineStr">
+      <c r="G27" s="13" t="inlineStr">
         <is>
           <t>normatif</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">  resultat financier</t>
         </is>
       </c>
-      <c r="C28" s="12" t="inlineStr">
+      <c r="C28" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D28" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E28" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F28" s="12" t="inlineStr">
+      <c r="F28" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G28" s="12" t="inlineStr">
+      <c r="G28" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -3058,7 +3403,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3116,23 +3461,23 @@
           <t>Chiffre d'affaires</t>
         </is>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="15">
         <f>IF(ABS(Modele!C3-Modele!I3)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!C3-Modele!I3,"0.00"))</f>
         <v/>
       </c>
-      <c r="C3" s="14">
+      <c r="C3" s="15">
         <f>IF(ABS(Modele!D3-Modele!J3)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!D3-Modele!J3,"0.00"))</f>
         <v/>
       </c>
-      <c r="D3" s="14">
+      <c r="D3" s="15">
         <f>IF(ABS(Modele!E3-Modele!K3)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!E3-Modele!K3,"0.00"))</f>
         <v/>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="15">
         <f>IF(ABS(Modele!F3-Modele!L3)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!F3-Modele!L3,"0.00"))</f>
         <v/>
       </c>
-      <c r="F3" s="14">
+      <c r="F3" s="15">
         <f>IF(ABS(Modele!G3-Modele!M3)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!G3-Modele!M3,"0.00"))</f>
         <v/>
       </c>
@@ -3143,23 +3488,23 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="15">
         <f>IF(ABS(Modele!C6-Modele!I6)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!C6-Modele!I6,"0.00"))</f>
         <v/>
       </c>
-      <c r="C4" s="14">
+      <c r="C4" s="15">
         <f>IF(ABS(Modele!D6-Modele!J6)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!D6-Modele!J6,"0.00"))</f>
         <v/>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="15">
         <f>IF(ABS(Modele!E6-Modele!K6)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!E6-Modele!K6,"0.00"))</f>
         <v/>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="15">
         <f>IF(ABS(Modele!F6-Modele!L6)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!F6-Modele!L6,"0.00"))</f>
         <v/>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="15">
         <f>IF(ABS(Modele!G6-Modele!M6)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!G6-Modele!M6,"0.00"))</f>
         <v/>
       </c>
@@ -3170,23 +3515,23 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="15">
         <f>IF(ABS(Modele!C10-Modele!I10)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!C10-Modele!I10,"0.00"))</f>
         <v/>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="15">
         <f>IF(ABS(Modele!D10-Modele!J10)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!D10-Modele!J10,"0.00"))</f>
         <v/>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="15">
         <f>IF(ABS(Modele!E10-Modele!K10)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!E10-Modele!K10,"0.00"))</f>
         <v/>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="15">
         <f>IF(ABS(Modele!F10-Modele!L10)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!F10-Modele!L10,"0.00"))</f>
         <v/>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="15">
         <f>IF(ABS(Modele!G10-Modele!M10)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!G10-Modele!M10,"0.00"))</f>
         <v/>
       </c>
@@ -3197,23 +3542,23 @@
           <t>Resultat avant impot</t>
         </is>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="15">
         <f>IF(ABS(Modele!C15-Modele!I15)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!C15-Modele!I15,"0.00"))</f>
         <v/>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="15">
         <f>IF(ABS(Modele!D15-Modele!J15)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!D15-Modele!J15,"0.00"))</f>
         <v/>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="15">
         <f>IF(ABS(Modele!E15-Modele!K15)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!E15-Modele!K15,"0.00"))</f>
         <v/>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="15">
         <f>IF(ABS(Modele!F15-Modele!L15)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!F15-Modele!L15,"0.00"))</f>
         <v/>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="15">
         <f>IF(ABS(Modele!G15-Modele!M15)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!G15-Modele!M15,"0.00"))</f>
         <v/>
       </c>
@@ -3224,23 +3569,23 @@
           <t>Impot</t>
         </is>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="15">
         <f>IF(ABS(Modele!C17-Modele!I17)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!C17-Modele!I17,"0.00"))</f>
         <v/>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="15">
         <f>IF(ABS(Modele!D17-Modele!J17)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!D17-Modele!J17,"0.00"))</f>
         <v/>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="15">
         <f>IF(ABS(Modele!E17-Modele!K17)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!E17-Modele!K17,"0.00"))</f>
         <v/>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="15">
         <f>IF(ABS(Modele!F17-Modele!L17)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!F17-Modele!L17,"0.00"))</f>
         <v/>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="15">
         <f>IF(ABS(Modele!G17-Modele!M17)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!G17-Modele!M17,"0.00"))</f>
         <v/>
       </c>
@@ -3251,23 +3596,23 @@
           <t>Resultat net</t>
         </is>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="15">
         <f>IF(ABS(Modele!C19-Modele!I19)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!C19-Modele!I19,"0.00"))</f>
         <v/>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="15">
         <f>IF(ABS(Modele!D19-Modele!J19)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!D19-Modele!J19,"0.00"))</f>
         <v/>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="15">
         <f>IF(ABS(Modele!E19-Modele!K19)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!E19-Modele!K19,"0.00"))</f>
         <v/>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="15">
         <f>IF(ABS(Modele!F19-Modele!L19)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!F19-Modele!L19,"0.00"))</f>
         <v/>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="15">
         <f>IF(ABS(Modele!G19-Modele!M19)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!G19-Modele!M19,"0.00"))</f>
         <v/>
       </c>
@@ -3278,23 +3623,23 @@
           <t>BPA</t>
         </is>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="15">
         <f>IF(ABS(Modele!C21-Modele!I21)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!C21-Modele!I21,"0.00"))</f>
         <v/>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="15">
         <f>IF(ABS(Modele!D21-Modele!J21)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!D21-Modele!J21,"0.00"))</f>
         <v/>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="15">
         <f>IF(ABS(Modele!E21-Modele!K21)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!E21-Modele!K21,"0.00"))</f>
         <v/>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="15">
         <f>IF(ABS(Modele!F21-Modele!L21)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!F21-Modele!L21,"0.00"))</f>
         <v/>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="15">
         <f>IF(ABS(Modele!G21-Modele!M21)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!G21-Modele!M21,"0.00"))</f>
         <v/>
       </c>
@@ -3312,7 +3657,7 @@
           <t>Aucune cellule orpheline (regle 5)</t>
         </is>
       </c>
-      <c r="B12" s="14">
+      <c r="B12" s="15">
         <f>IF(COUNTBLANK(Hypotheses!$C$3:$C$27)=0,"OK","MOTEUR MANQUANT")</f>
         <v/>
       </c>
@@ -3323,13 +3668,13 @@
           <t>Devise de reporting = devise de cotation (prop. 6)</t>
         </is>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="15">
         <f>IF(EXACT('Lisez-moi'!B10,'Lisez-moi'!B11),"OK","P/E INTERDIT SANS TAUX DATE")</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Colonne 'moteur' de la feuille Modele = valeur produite par engine/model.py. Toute divergence est une erreur de traduction, pas une tolerance.</t>
         </is>

--- a/artifacts/SYNTHETIQUE.xlsx
+++ b/artifacts/SYNTHETIQUE.xlsx
@@ -164,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -198,6 +198,9 @@
     <xf numFmtId="4" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2348,7 +2351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3396,6 +3399,687 @@
         <is>
           <t>2</t>
         </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>LES MEMES CELLULES, EN FORMULES — ce a quoi chaque chiffre fait reference</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n"/>
+      <c r="C30" s="4" t="n"/>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="n"/>
+      <c r="G30" s="4" t="n"/>
+      <c r="H30" s="4" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>ligne</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>cellule</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>2027</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>2028</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>2029</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>Chiffre d'affaires</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>ligne 3</t>
+        </is>
+      </c>
+      <c r="C32" s="27">
+        <f>B3*(1+g_2026)</f>
+        <v/>
+      </c>
+      <c r="D32" s="27">
+        <f>C3*(1+g_2027)</f>
+        <v/>
+      </c>
+      <c r="E32" s="27">
+        <f>D3*(1+g_2028)</f>
+        <v/>
+      </c>
+      <c r="F32" s="27">
+        <f>E3*(1+g_2029)</f>
+        <v/>
+      </c>
+      <c r="G32" s="27">
+        <f>F3*(1+g_2030)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>Croissance</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>ligne 4</t>
+        </is>
+      </c>
+      <c r="C33" s="27">
+        <f>g_2026</f>
+        <v/>
+      </c>
+      <c r="D33" s="27">
+        <f>g_2027</f>
+        <v/>
+      </c>
+      <c r="E33" s="27">
+        <f>g_2028</f>
+        <v/>
+      </c>
+      <c r="F33" s="27">
+        <f>g_2029</f>
+        <v/>
+      </c>
+      <c r="G33" s="27">
+        <f>g_2030</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>Marge d'EBITDA</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>ligne 5</t>
+        </is>
+      </c>
+      <c r="C34" s="27">
+        <f>marge_2026</f>
+        <v/>
+      </c>
+      <c r="D34" s="27">
+        <f>marge_2027</f>
+        <v/>
+      </c>
+      <c r="E34" s="27">
+        <f>marge_2028</f>
+        <v/>
+      </c>
+      <c r="F34" s="27">
+        <f>marge_2029</f>
+        <v/>
+      </c>
+      <c r="G34" s="27">
+        <f>marge_2030</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>ligne 6</t>
+        </is>
+      </c>
+      <c r="C35" s="27">
+        <f>C3*C5</f>
+        <v/>
+      </c>
+      <c r="D35" s="27">
+        <f>D3*D5</f>
+        <v/>
+      </c>
+      <c r="E35" s="27">
+        <f>E3*E5</f>
+        <v/>
+      </c>
+      <c r="F35" s="27">
+        <f>F3*F5</f>
+        <v/>
+      </c>
+      <c r="G35" s="27">
+        <f>G3*G5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>dotations hors PPA</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>ligne 7</t>
+        </is>
+      </c>
+      <c r="C36" s="27">
+        <f>B7+B3*capexRatio/dureeAmort</f>
+        <v/>
+      </c>
+      <c r="D36" s="27">
+        <f>C7+C3*capexRatio/dureeAmort</f>
+        <v/>
+      </c>
+      <c r="E36" s="27">
+        <f>D7+D3*capexRatio/dureeAmort</f>
+        <v/>
+      </c>
+      <c r="F36" s="27">
+        <f>E7+E3*capexRatio/dureeAmort</f>
+        <v/>
+      </c>
+      <c r="G36" s="27">
+        <f>F7+F3*capexRatio/dureeAmort</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>amortissement du PPA</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>ligne 8</t>
+        </is>
+      </c>
+      <c r="C37" s="27">
+        <f>30.0</f>
+        <v/>
+      </c>
+      <c r="D37" s="27">
+        <f>28.0</f>
+        <v/>
+      </c>
+      <c r="E37" s="27">
+        <f>24.0</f>
+        <v/>
+      </c>
+      <c r="F37" s="27">
+        <f>18.0</f>
+        <v/>
+      </c>
+      <c r="G37" s="27">
+        <f>10.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>Dotations</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>ligne 9</t>
+        </is>
+      </c>
+      <c r="C38" s="27">
+        <f>-(C7+C8)</f>
+        <v/>
+      </c>
+      <c r="D38" s="27">
+        <f>-(D7+D8)</f>
+        <v/>
+      </c>
+      <c r="E38" s="27">
+        <f>-(E7+E8)</f>
+        <v/>
+      </c>
+      <c r="F38" s="27">
+        <f>-(F7+F8)</f>
+        <v/>
+      </c>
+      <c r="G38" s="27">
+        <f>-(G7+G8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>ligne 10</t>
+        </is>
+      </c>
+      <c r="C39" s="27">
+        <f>C6+C9</f>
+        <v/>
+      </c>
+      <c r="D39" s="27">
+        <f>D6+D9</f>
+        <v/>
+      </c>
+      <c r="E39" s="27">
+        <f>E6+E9</f>
+        <v/>
+      </c>
+      <c r="F39" s="27">
+        <f>F6+F9</f>
+        <v/>
+      </c>
+      <c r="G39" s="27">
+        <f>G6+G9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>Dette brute</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>ligne 11</t>
+        </is>
+      </c>
+      <c r="C40" s="27">
+        <f>B11</f>
+        <v/>
+      </c>
+      <c r="D40" s="27">
+        <f>C11</f>
+        <v/>
+      </c>
+      <c r="E40" s="27">
+        <f>D11</f>
+        <v/>
+      </c>
+      <c r="F40" s="27">
+        <f>E11</f>
+        <v/>
+      </c>
+      <c r="G40" s="27">
+        <f>F11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>Tresorerie</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>ligne 12</t>
+        </is>
+      </c>
+      <c r="C41" s="27">
+        <f>B12</f>
+        <v/>
+      </c>
+      <c r="D41" s="27">
+        <f>C12</f>
+        <v/>
+      </c>
+      <c r="E41" s="27">
+        <f>D12</f>
+        <v/>
+      </c>
+      <c r="F41" s="27">
+        <f>E12</f>
+        <v/>
+      </c>
+      <c r="G41" s="27">
+        <f>F12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>Dette locative</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>ligne 13</t>
+        </is>
+      </c>
+      <c r="C42" s="27">
+        <f>B13</f>
+        <v/>
+      </c>
+      <c r="D42" s="27">
+        <f>C13</f>
+        <v/>
+      </c>
+      <c r="E42" s="27">
+        <f>D13</f>
+        <v/>
+      </c>
+      <c r="F42" s="27">
+        <f>E13</f>
+        <v/>
+      </c>
+      <c r="G42" s="27">
+        <f>F13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>Resultat financier (rang 2)</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="inlineStr">
+        <is>
+          <t>ligne 14</t>
+        </is>
+      </c>
+      <c r="C43" s="27">
+        <f>-(B11*tauxDette)+B12*tauxCash-(B13*tauxLease)</f>
+        <v/>
+      </c>
+      <c r="D43" s="27">
+        <f>-(C11*tauxDette)+C12*tauxCash-(C13*tauxLease)</f>
+        <v/>
+      </c>
+      <c r="E43" s="27">
+        <f>-(D11*tauxDette)+D12*tauxCash-(D13*tauxLease)</f>
+        <v/>
+      </c>
+      <c r="F43" s="27">
+        <f>-(E11*tauxDette)+E12*tauxCash-(E13*tauxLease)</f>
+        <v/>
+      </c>
+      <c r="G43" s="27">
+        <f>-(F11*tauxDette)+F12*tauxCash-(F13*tauxLease)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>Resultat avant impot</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>ligne 15</t>
+        </is>
+      </c>
+      <c r="C44" s="27">
+        <f>C10+C14</f>
+        <v/>
+      </c>
+      <c r="D44" s="27">
+        <f>D10+D14</f>
+        <v/>
+      </c>
+      <c r="E44" s="27">
+        <f>E10+E14</f>
+        <v/>
+      </c>
+      <c r="F44" s="27">
+        <f>F10+F14</f>
+        <v/>
+      </c>
+      <c r="G44" s="27">
+        <f>G10+G14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>Taux d'impot applique</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>ligne 16</t>
+        </is>
+      </c>
+      <c r="C45" s="27">
+        <f>tauxIS_2026</f>
+        <v/>
+      </c>
+      <c r="D45" s="27">
+        <f>tauxIS_2027</f>
+        <v/>
+      </c>
+      <c r="E45" s="27">
+        <f>tauxIS_2028</f>
+        <v/>
+      </c>
+      <c r="F45" s="27">
+        <f>tauxIS_2029</f>
+        <v/>
+      </c>
+      <c r="G45" s="27">
+        <f>tauxIS_2030</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>Impot</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>ligne 17</t>
+        </is>
+      </c>
+      <c r="C46" s="27">
+        <f>-C15*C16</f>
+        <v/>
+      </c>
+      <c r="D46" s="27">
+        <f>-D15*D16</f>
+        <v/>
+      </c>
+      <c r="E46" s="27">
+        <f>-E15*E16</f>
+        <v/>
+      </c>
+      <c r="F46" s="27">
+        <f>-F15*F16</f>
+        <v/>
+      </c>
+      <c r="G46" s="27">
+        <f>-G15*G16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>Minoritaires</t>
+        </is>
+      </c>
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>ligne 18</t>
+        </is>
+      </c>
+      <c r="C47" s="27">
+        <f>partMinos*(C15+C17)</f>
+        <v/>
+      </c>
+      <c r="D47" s="27">
+        <f>partMinos*(D15+D17)</f>
+        <v/>
+      </c>
+      <c r="E47" s="27">
+        <f>partMinos*(E15+E17)</f>
+        <v/>
+      </c>
+      <c r="F47" s="27">
+        <f>partMinos*(F15+F17)</f>
+        <v/>
+      </c>
+      <c r="G47" s="27">
+        <f>partMinos*(G15+G17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>Resultat net</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>ligne 19</t>
+        </is>
+      </c>
+      <c r="C48" s="27">
+        <f>C15+C17+C18</f>
+        <v/>
+      </c>
+      <c r="D48" s="27">
+        <f>D15+D17+D18</f>
+        <v/>
+      </c>
+      <c r="E48" s="27">
+        <f>E15+E17+E18</f>
+        <v/>
+      </c>
+      <c r="F48" s="27">
+        <f>F15+F17+F18</f>
+        <v/>
+      </c>
+      <c r="G48" s="27">
+        <f>G15+G17+G18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>Actions (millions)</t>
+        </is>
+      </c>
+      <c r="B49" s="13" t="inlineStr">
+        <is>
+          <t>ligne 20</t>
+        </is>
+      </c>
+      <c r="C49" s="27">
+        <f>B20*(1-rachatPct)</f>
+        <v/>
+      </c>
+      <c r="D49" s="27">
+        <f>C20*(1-rachatPct)</f>
+        <v/>
+      </c>
+      <c r="E49" s="27">
+        <f>D20*(1-rachatPct)</f>
+        <v/>
+      </c>
+      <c r="F49" s="27">
+        <f>E20*(1-rachatPct)</f>
+        <v/>
+      </c>
+      <c r="G49" s="27">
+        <f>F20*(1-rachatPct)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>BPA</t>
+        </is>
+      </c>
+      <c r="B50" s="13" t="inlineStr">
+        <is>
+          <t>ligne 21</t>
+        </is>
+      </c>
+      <c r="C50" s="27">
+        <f>C19/C20</f>
+        <v/>
+      </c>
+      <c r="D50" s="27">
+        <f>D19/D20</f>
+        <v/>
+      </c>
+      <c r="E50" s="27">
+        <f>E19/E20</f>
+        <v/>
+      </c>
+      <c r="F50" s="27">
+        <f>F19/F20</f>
+        <v/>
+      </c>
+      <c r="G50" s="27">
+        <f>G19/G20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>Dividende verse</t>
+        </is>
+      </c>
+      <c r="B51" s="13" t="inlineStr">
+        <is>
+          <t>ligne 22</t>
+        </is>
+      </c>
+      <c r="C51" s="27">
+        <f>C19*tauxDistrib</f>
+        <v/>
+      </c>
+      <c r="D51" s="27">
+        <f>D19*tauxDistrib</f>
+        <v/>
+      </c>
+      <c r="E51" s="27">
+        <f>E19*tauxDistrib</f>
+        <v/>
+      </c>
+      <c r="F51" s="27">
+        <f>F19*tauxDistrib</f>
+        <v/>
+      </c>
+      <c r="G51" s="27">
+        <f>G19*tauxDistrib</f>
+        <v/>
       </c>
     </row>
   </sheetData>
